--- a/数据表/Datas/ItemConfig_物品配置.xlsx
+++ b/数据表/Datas/ItemConfig_物品配置.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="56">
   <si>
     <t>##var</t>
   </si>
@@ -65,6 +65,9 @@
     <t>speedBonus</t>
   </si>
   <si>
+    <t>icon</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -83,6 +86,9 @@
     <t>EquipmentSlotType</t>
   </si>
   <si>
+    <t>string#ref=TbSpriteConfig</t>
+  </si>
+  <si>
     <t>##group</t>
   </si>
   <si>
@@ -93,6 +99,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
       <t>物品</t>
     </r>
     <r>
@@ -106,19 +118,59 @@
     </r>
   </si>
   <si>
-    <t>原型名</t>
-  </si>
-  <si>
-    <t>物品类型</t>
-  </si>
-  <si>
-    <t>稀有度</t>
-  </si>
-  <si>
-    <t>单格堆叠上限</t>
-  </si>
-  <si>
-    <t>装备栏类型</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>原型名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>物品类型</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>稀有度</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单格堆叠上限</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>装备栏类型</t>
+    </r>
   </si>
   <si>
     <r>
@@ -183,14 +235,34 @@
     <r>
       <rPr>
         <sz val="12"/>
-        <rFont val="宋体-简"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
         <charset val="134"/>
       </rPr>
       <t>修正</t>
     </r>
   </si>
   <si>
-    <t>旧硬币</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>图标资源配置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>旧硬币</t>
+    </r>
   </si>
   <si>
     <t>Loot</t>
@@ -202,31 +274,71 @@
     <t>None</t>
   </si>
   <si>
-    <t>宝石碎片</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石碎片</t>
+    </r>
   </si>
   <si>
     <t>Green</t>
   </si>
   <si>
-    <t>古代零件</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>古代零件</t>
+    </r>
   </si>
   <si>
     <t>Blue</t>
   </si>
   <si>
-    <t>精致核心</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>精致核心</t>
+    </r>
   </si>
   <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>神秘遗物</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>神秘遗物</t>
+    </r>
   </si>
   <si>
     <t>Red</t>
   </si>
   <si>
-    <t>训练剑</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>训练剑</t>
+    </r>
   </si>
   <si>
     <t>Equipment</t>
@@ -235,19 +347,51 @@
     <t>Weapon</t>
   </si>
   <si>
-    <t>法杖</t>
-  </si>
-  <si>
-    <t>布甲</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>法杖</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>布甲</t>
+    </r>
   </si>
   <si>
     <t>Armor</t>
   </si>
   <si>
-    <t>术士长袍</t>
-  </si>
-  <si>
-    <t>恢复药</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>术士长袍</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="PingFang SC Regular"/>
+        <charset val="134"/>
+      </rPr>
+      <t>恢复药</t>
+    </r>
   </si>
   <si>
     <t>Consumable</t>
@@ -263,7 +407,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -300,20 +444,8 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <color rgb="FF202020"/>
       <name val="Andale Mono"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
     <font>
@@ -469,11 +601,18 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="宋体-简"/>
+      <color rgb="FF202020"/>
+      <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="PingFang SC Regular"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -525,18 +664,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -874,22 +1001,31 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -898,46 +1034,43 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -949,81 +1082,75 @@
     <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1041,13 +1168,7 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1521,7 +1642,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -1536,10 +1657,11 @@
     <col min="10" max="10" width="12.7352941176471" style="1" customWidth="1"/>
     <col min="11" max="11" width="10" style="1" customWidth="1"/>
     <col min="12" max="12" width="12.5" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="13" max="13" width="33.2058823529412" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" customHeight="1" spans="1:12">
+    <row r="1" customHeight="1" spans="1:13">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1576,477 +1698,517 @@
       <c r="L1" s="3" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" customHeight="1" spans="1:12">
+    <row r="2" customHeight="1" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>13</v>
-      </c>
       <c r="G2" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="M2" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="1:12">
+    <row r="3" customHeight="1" spans="1:13">
       <c r="A3" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L3" s="5"/>
+      <c r="M3" s="5"/>
     </row>
-    <row r="4" customHeight="1" spans="1:12">
+    <row r="4" customHeight="1" spans="1:13">
       <c r="A4" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:13">
+      <c r="A5" s="7"/>
+      <c r="B5" s="7">
+        <v>5001</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F5" s="7">
+        <v>99</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0</v>
+      </c>
+      <c r="I5" s="7">
+        <v>0</v>
+      </c>
+      <c r="J5" s="7">
+        <v>0</v>
+      </c>
+      <c r="K5" s="7">
+        <v>0</v>
+      </c>
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" customHeight="1" spans="1:13">
+      <c r="A6" s="7"/>
+      <c r="B6" s="7">
+        <v>5002</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F6" s="7">
+        <v>99</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7">
+        <v>0</v>
+      </c>
+      <c r="J6" s="7">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1">
+        <v>0</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:13">
+      <c r="A7" s="7"/>
+      <c r="B7" s="7">
+        <v>5003</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="7">
+        <v>99</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" s="7">
+        <v>0</v>
+      </c>
+      <c r="I7" s="7">
+        <v>0</v>
+      </c>
+      <c r="J7" s="7">
+        <v>0</v>
+      </c>
+      <c r="K7" s="7">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1">
+        <v>0</v>
+      </c>
+      <c r="M7" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:13">
+      <c r="A8" s="7"/>
+      <c r="B8" s="7">
+        <v>5004</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="7">
+        <v>99</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0</v>
+      </c>
+      <c r="I8" s="7">
+        <v>0</v>
+      </c>
+      <c r="J8" s="7">
+        <v>0</v>
+      </c>
+      <c r="K8" s="7">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1">
+        <v>0</v>
+      </c>
+      <c r="M8" s="7" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:13">
+      <c r="A9" s="7"/>
+      <c r="B9" s="7">
+        <v>5005</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="7">
+        <v>99</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0</v>
+      </c>
+      <c r="I9" s="7">
+        <v>0</v>
+      </c>
+      <c r="J9" s="7">
+        <v>0</v>
+      </c>
+      <c r="K9" s="7">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1">
+        <v>0</v>
+      </c>
+      <c r="M9" s="7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:13">
+      <c r="A10" s="7"/>
+      <c r="B10" s="7">
+        <v>5101</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" s="7">
+        <v>1</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H10" s="7">
+        <v>0</v>
+      </c>
+      <c r="I10" s="7">
+        <v>0</v>
+      </c>
+      <c r="J10" s="7">
+        <v>5</v>
+      </c>
+      <c r="K10" s="7">
+        <v>0</v>
+      </c>
+      <c r="L10" s="1">
+        <v>0</v>
+      </c>
+      <c r="M10" s="7" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:13">
+      <c r="A11" s="7"/>
+      <c r="B11" s="7">
+        <v>5102</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="7">
+        <v>1</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0</v>
+      </c>
+      <c r="I11" s="7">
+        <v>10</v>
+      </c>
+      <c r="J11" s="7">
+        <v>0</v>
+      </c>
+      <c r="K11" s="7">
+        <v>8</v>
+      </c>
+      <c r="L11" s="1">
+        <v>0</v>
+      </c>
+      <c r="M11" s="7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:13">
+      <c r="A12" s="7"/>
+      <c r="B12" s="7">
+        <v>5201</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="7">
+        <v>1</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H12" s="7">
         <v>20</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" customHeight="1" spans="1:12">
-      <c r="A5" s="8"/>
-      <c r="B5" s="8">
-        <v>5001</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="8">
-        <v>99</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H5" s="8">
-        <v>0</v>
-      </c>
-      <c r="I5" s="8">
-        <v>0</v>
-      </c>
-      <c r="J5" s="8">
-        <v>0</v>
-      </c>
-      <c r="K5" s="8">
-        <v>0</v>
-      </c>
-      <c r="L5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:12">
-      <c r="A6" s="8"/>
-      <c r="B6" s="8">
-        <v>5002</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F6" s="8">
-        <v>99</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H6" s="8">
-        <v>0</v>
-      </c>
-      <c r="I6" s="8">
-        <v>0</v>
-      </c>
-      <c r="J6" s="8">
-        <v>0</v>
-      </c>
-      <c r="K6" s="8">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:12">
-      <c r="A7" s="8"/>
-      <c r="B7" s="8">
-        <v>5003</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="8">
-        <v>99</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H7" s="8">
-        <v>0</v>
-      </c>
-      <c r="I7" s="8">
-        <v>0</v>
-      </c>
-      <c r="J7" s="8">
-        <v>0</v>
-      </c>
-      <c r="K7" s="8">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:12">
-      <c r="A8" s="8"/>
-      <c r="B8" s="8">
-        <v>5004</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="8">
-        <v>99</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H8" s="8">
-        <v>0</v>
-      </c>
-      <c r="I8" s="8">
-        <v>0</v>
-      </c>
-      <c r="J8" s="8">
-        <v>0</v>
-      </c>
-      <c r="K8" s="8">
-        <v>0</v>
-      </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:12">
-      <c r="A9" s="8"/>
-      <c r="B9" s="8">
-        <v>5005</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="8">
-        <v>99</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H9" s="8">
-        <v>0</v>
-      </c>
-      <c r="I9" s="8">
-        <v>0</v>
-      </c>
-      <c r="J9" s="8">
-        <v>0</v>
-      </c>
-      <c r="K9" s="8">
-        <v>0</v>
-      </c>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:12">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8">
-        <v>5101</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="8">
-        <v>1</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H10" s="8">
-        <v>0</v>
-      </c>
-      <c r="I10" s="8">
-        <v>0</v>
-      </c>
-      <c r="J10" s="8">
-        <v>5</v>
-      </c>
-      <c r="K10" s="8">
-        <v>0</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:12">
-      <c r="A11" s="8"/>
-      <c r="B11" s="8">
-        <v>5102</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>47</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>39</v>
-      </c>
-      <c r="F11" s="8">
-        <v>1</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="8">
-        <v>0</v>
-      </c>
-      <c r="I11" s="8">
-        <v>10</v>
-      </c>
-      <c r="J11" s="8">
-        <v>0</v>
-      </c>
-      <c r="K11" s="8">
-        <v>8</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:12">
-      <c r="A12" s="8"/>
-      <c r="B12" s="8">
-        <v>5201</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="8">
-        <v>1</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="H12" s="8">
-        <v>20</v>
-      </c>
-      <c r="I12" s="8">
-        <v>0</v>
-      </c>
-      <c r="J12" s="8">
-        <v>0</v>
-      </c>
-      <c r="K12" s="8">
+      <c r="I12" s="7">
+        <v>0</v>
+      </c>
+      <c r="J12" s="7">
+        <v>0</v>
+      </c>
+      <c r="K12" s="7">
         <v>0</v>
       </c>
       <c r="L12" s="1">
         <v>1</v>
       </c>
+      <c r="M12" s="7" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="13" customHeight="1" spans="1:12">
-      <c r="A13" s="8"/>
-      <c r="B13" s="8">
+    <row r="13" customHeight="1" spans="1:13">
+      <c r="A13" s="7"/>
+      <c r="B13" s="7">
         <v>5202</v>
       </c>
-      <c r="C13" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="F13" s="8">
+      <c r="C13" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F13" s="7">
         <v>1</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="H13" s="8">
+      <c r="G13" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="7">
         <v>10</v>
       </c>
-      <c r="I13" s="8">
+      <c r="I13" s="7">
         <v>30</v>
       </c>
-      <c r="J13" s="8">
-        <v>0</v>
-      </c>
-      <c r="K13" s="8">
+      <c r="J13" s="7">
+        <v>0</v>
+      </c>
+      <c r="K13" s="7">
         <v>5</v>
       </c>
       <c r="L13" s="1">
         <v>0</v>
       </c>
+      <c r="M13" s="7" t="s">
+        <v>53</v>
+      </c>
     </row>
-    <row r="14" customHeight="1" spans="1:12">
-      <c r="A14" s="8"/>
-      <c r="B14" s="8">
+    <row r="14" customHeight="1" spans="1:13">
+      <c r="A14" s="7"/>
+      <c r="B14" s="7">
         <v>5301</v>
       </c>
-      <c r="C14" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="8">
+      <c r="C14" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="7">
         <v>10</v>
       </c>
-      <c r="G14" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="H14" s="8">
-        <v>0</v>
-      </c>
-      <c r="I14" s="8">
-        <v>0</v>
-      </c>
-      <c r="J14" s="8">
-        <v>0</v>
-      </c>
-      <c r="K14" s="8">
+      <c r="G14" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="7">
+        <v>0</v>
+      </c>
+      <c r="I14" s="7">
+        <v>0</v>
+      </c>
+      <c r="J14" s="7">
+        <v>0</v>
+      </c>
+      <c r="K14" s="7">
         <v>0</v>
       </c>
       <c r="L14" s="1">
         <v>0</v>
+      </c>
+      <c r="M14" s="7" t="s">
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/数据表/Datas/ItemConfig_物品配置.xlsx
+++ b/数据表/Datas/ItemConfig_物品配置.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16080"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -174,6 +174,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>HP</t>
     </r>
     <r>
@@ -188,6 +194,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>MP</t>
     </r>
     <r>
@@ -202,6 +214,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>ATK</t>
     </r>
     <r>
@@ -216,6 +234,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>MAT</t>
     </r>
     <r>
@@ -230,6 +254,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF9C0006"/>
+        <rFont val="Andale Mono"/>
+        <charset val="134"/>
+      </rPr>
       <t>SPD</t>
     </r>
     <r>
@@ -601,13 +631,13 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF202020"/>
+      <color rgb="FF9C0006"/>
       <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF202020"/>
       <name val="PingFang SC Regular"/>
       <charset val="134"/>
     </font>
@@ -1651,7 +1681,7 @@
     <col min="4" max="4" width="13.9705882352941" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.4926470588235" style="1" customWidth="1"/>
     <col min="6" max="6" width="13.6029411764706" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.3970588235294" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24.3823529411765" style="1" customWidth="1"/>
     <col min="8" max="8" width="11.3970588235294" style="1" customWidth="1"/>
     <col min="9" max="9" width="12" style="1" customWidth="1"/>
     <col min="10" max="10" width="12.7352941176471" style="1" customWidth="1"/>

--- a/数据表/Datas/ItemConfig_物品配置.xlsx
+++ b/数据表/Datas/ItemConfig_物品配置.xlsx
@@ -1,13 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Seek-Battle-Evacuate\数据表\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="16660"/>
+    <workbookView windowWidth="24750" windowHeight="12080" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="常规" sheetId="1" r:id="rId1"/>
+    <sheet name="武器" sheetId="2" r:id="rId2"/>
+    <sheet name="防具" sheetId="3" r:id="rId3"/>
+    <sheet name="消耗品" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="137">
   <si>
     <t>##var</t>
   </si>
@@ -102,7 +110,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>物品</t>
@@ -111,7 +119,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
+        <rFont val="Consolas"/>
         <charset val="134"/>
       </rPr>
       <t>ID</t>
@@ -122,7 +130,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>原型名</t>
@@ -133,7 +141,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>物品类型</t>
@@ -144,7 +152,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>稀有度</t>
@@ -155,7 +163,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>单格堆叠上限</t>
@@ -166,7 +174,7 @@
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>装备栏类型</t>
@@ -174,19 +182,27 @@
   </si>
   <si>
     <r>
+      <t>HP</t>
+    </r>
+    <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>HP</t>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>上限修正</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>MP</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
+        <rFont val="微软雅黑"/>
         <charset val="134"/>
       </rPr>
       <t>上限修正</t>
@@ -194,237 +210,1701 @@
   </si>
   <si>
     <r>
+      <t>ATK</t>
+    </r>
+    <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>MP</t>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>修正</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>MAT</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>上限修正</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>修正</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>SPD</t>
+    </r>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ATK</t>
-    </r>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>修正</t>
+    </r>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>修正</t>
-    </r>
-  </si>
-  <si>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>图标资源配置</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>##</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>常规</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>铜币</t>
+    </r>
+  </si>
+  <si>
+    <t>Loot</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>银币</t>
+    </r>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>金币</t>
+    </r>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>铂币</t>
+    </r>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>全币</t>
+    </r>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> V</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VIII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>骨头</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IX</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> V</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VIII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>符文</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IX</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> V</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VIII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>种子</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IX</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> V</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VIII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>宝石</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IX</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> V</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VI</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> VIII</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>收集品</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IX</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>短剑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>Weapon</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>短剑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>短剑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>菜刀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>菜刀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>菜刀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>阔剑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>阔剑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>阔剑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大法杖</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头盔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <t>Armor</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头盔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头盔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头盔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>头盔</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> V</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>术士长袍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> I</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>术士长袍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> II</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>术士长袍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> III</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>术士长袍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> IV</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>术士长袍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> V</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>物品</t>
+    </r>
     <r>
       <rPr>
         <sz val="12"/>
         <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>MAT</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>修正</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="Andale Mono"/>
-        <charset val="134"/>
-      </rPr>
-      <t>SPD</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>修正</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF9C0006"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>图标资源配置</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>旧硬币</t>
-    </r>
-  </si>
-  <si>
-    <t>Loot</t>
-  </si>
-  <si>
-    <t>White</t>
-  </si>
-  <si>
-    <t>None</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>宝石碎片</t>
-    </r>
-  </si>
-  <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>古代零件</t>
-    </r>
-  </si>
-  <si>
-    <t>Blue</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>精致核心</t>
-    </r>
-  </si>
-  <si>
-    <t>Gold</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>神秘遗物</t>
-    </r>
-  </si>
-  <si>
-    <t>Red</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>训练剑</t>
-    </r>
-  </si>
-  <si>
-    <t>Equipment</t>
-  </si>
-  <si>
-    <t>Weapon</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>法杖</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>布甲</t>
-    </r>
-  </si>
-  <si>
-    <t>Armor</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>术士长袍</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF202020"/>
-        <rFont val="PingFang SC Regular"/>
-        <charset val="134"/>
-      </rPr>
-      <t>恢复药</t>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ID</t>
+    </r>
+  </si>
+  <si>
+    <t>原型名</t>
+  </si>
+  <si>
+    <t>物品类型</t>
+  </si>
+  <si>
+    <t>稀有度</t>
+  </si>
+  <si>
+    <t>单格堆叠上限</t>
+  </si>
+  <si>
+    <t>装备栏类型</t>
+  </si>
+  <si>
+    <t>图标资源配置</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF202020"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>小药</t>
     </r>
   </si>
   <si>
     <t>Consumable</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中小药</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中药</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>中大药</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <rFont val="微软雅黑"/>
+        <charset val="134"/>
+      </rPr>
+      <t>大药</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -437,7 +1917,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -445,37 +1925,43 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF006100"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F4E78"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF595959"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF9C0006"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -631,14 +2117,13 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
+      <color rgb="FF202020"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF202020"/>
-      <name val="PingFang SC Regular"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1034,31 +2519,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1067,139 +2549,176 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="4" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="50">
@@ -1672,577 +3191,4144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:M61"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="10.6617647058824" style="1" customWidth="1"/>
-    <col min="3" max="3" width="11.6397058823529" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.9705882352941" style="1" customWidth="1"/>
-    <col min="5" max="5" width="12.4926470588235" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.6029411764706" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.3823529411765" style="1" customWidth="1"/>
-    <col min="8" max="8" width="11.3970588235294" style="1" customWidth="1"/>
-    <col min="9" max="9" width="12" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7352941176471" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5" style="1" customWidth="1"/>
-    <col min="13" max="13" width="33.2058823529412" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="11.4166666666667" style="15" customWidth="1"/>
+    <col min="2" max="2" width="10.6583333333333" style="14" customWidth="1"/>
+    <col min="3" max="3" width="12.8333333333333" style="14" customWidth="1"/>
+    <col min="4" max="4" width="15.4166666666667" style="14" customWidth="1"/>
+    <col min="5" max="5" width="14.3333333333333" style="14" customWidth="1"/>
+    <col min="6" max="6" width="14.75" style="14" customWidth="1"/>
+    <col min="7" max="7" width="24.3833333333333" style="14" customWidth="1"/>
+    <col min="8" max="8" width="11.4" style="14" customWidth="1"/>
+    <col min="9" max="9" width="12" style="14" customWidth="1"/>
+    <col min="10" max="10" width="12.7333333333333" style="14" customWidth="1"/>
+    <col min="11" max="11" width="10" style="14" customWidth="1"/>
+    <col min="12" max="12" width="12.5" style="14" customWidth="1"/>
+    <col min="13" max="13" width="29.3333333333333" style="14" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:13">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:13">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:13">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="K3" s="5" t="s">
+      <c r="K3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
     </row>
     <row r="4" customHeight="1" spans="1:13">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="11" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:13">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7">
+      <c r="A5" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="13"/>
+    </row>
+    <row r="6" customHeight="1" spans="1:13">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13">
         <v>5001</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="C6" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="D6" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F5" s="7">
+      <c r="E6" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="13">
         <v>99</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G6" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="13">
+        <v>0</v>
+      </c>
+      <c r="I6" s="13">
+        <v>0</v>
+      </c>
+      <c r="J6" s="13">
+        <v>0</v>
+      </c>
+      <c r="K6" s="13">
+        <v>0</v>
+      </c>
+      <c r="L6" s="14">
+        <v>0</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:13">
+      <c r="A7" s="12"/>
+      <c r="B7" s="13">
+        <v>5002</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="13">
+        <v>60</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="13">
+        <v>0</v>
+      </c>
+      <c r="I7" s="13">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13">
+        <v>0</v>
+      </c>
+      <c r="K7" s="13">
+        <v>0</v>
+      </c>
+      <c r="L7" s="14">
+        <v>0</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:13">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13">
+        <v>5003</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="13">
+        <v>40</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="13">
+        <v>0</v>
+      </c>
+      <c r="I8" s="13">
+        <v>0</v>
+      </c>
+      <c r="J8" s="13">
+        <v>0</v>
+      </c>
+      <c r="K8" s="13">
+        <v>0</v>
+      </c>
+      <c r="L8" s="14">
+        <v>0</v>
+      </c>
+      <c r="M8" s="13" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:13">
+      <c r="A9" s="12"/>
+      <c r="B9" s="13">
+        <v>5004</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="13">
+        <v>20</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="13">
+        <v>0</v>
+      </c>
+      <c r="I9" s="13">
+        <v>0</v>
+      </c>
+      <c r="J9" s="13">
+        <v>0</v>
+      </c>
+      <c r="K9" s="13">
+        <v>0</v>
+      </c>
+      <c r="L9" s="14">
+        <v>0</v>
+      </c>
+      <c r="M9" s="13" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:13">
+      <c r="A10" s="12"/>
+      <c r="B10" s="13">
+        <v>5005</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="13">
+        <v>1</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="13">
+        <v>0</v>
+      </c>
+      <c r="I10" s="13">
+        <v>0</v>
+      </c>
+      <c r="J10" s="13">
+        <v>0</v>
+      </c>
+      <c r="K10" s="13">
+        <v>0</v>
+      </c>
+      <c r="L10" s="14">
+        <v>0</v>
+      </c>
+      <c r="M10" s="13" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:13">
+      <c r="A11" s="12"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="M11" s="13"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:13">
+      <c r="A12" s="12"/>
+      <c r="B12" s="13">
+        <v>5006</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="H5" s="7">
-        <v>0</v>
-      </c>
-      <c r="I5" s="7">
-        <v>0</v>
-      </c>
-      <c r="J5" s="7">
-        <v>0</v>
-      </c>
-      <c r="K5" s="7">
-        <v>0</v>
-      </c>
-      <c r="L5" s="1">
-        <v>0</v>
-      </c>
-      <c r="M5" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" customHeight="1" spans="1:13">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7">
-        <v>5002</v>
-      </c>
-      <c r="C6" s="7" t="s">
+      <c r="F12" s="13">
+        <v>99</v>
+      </c>
+      <c r="G12" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="H12" s="13">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13">
+        <v>0</v>
+      </c>
+      <c r="K12" s="13">
+        <v>0</v>
+      </c>
+      <c r="L12" s="13">
+        <v>0</v>
+      </c>
+      <c r="M12" s="13" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:13">
+      <c r="A13" s="12"/>
+      <c r="B13" s="13">
+        <v>5007</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="13">
+        <v>99</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="13">
+        <v>0</v>
+      </c>
+      <c r="I13" s="13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="13">
+        <v>0</v>
+      </c>
+      <c r="L13" s="13">
+        <v>0</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:13">
+      <c r="A14" s="12"/>
+      <c r="B14" s="13">
+        <v>5008</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F14" s="13">
+        <v>99</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="13">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13">
+        <v>0</v>
+      </c>
+      <c r="J14" s="13">
+        <v>0</v>
+      </c>
+      <c r="K14" s="13">
+        <v>0</v>
+      </c>
+      <c r="L14" s="13">
+        <v>0</v>
+      </c>
+      <c r="M14" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:13">
+      <c r="A15" s="12"/>
+      <c r="B15" s="13">
+        <v>5009</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F15" s="13">
+        <v>99</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H15" s="13">
+        <v>0</v>
+      </c>
+      <c r="I15" s="13">
+        <v>0</v>
+      </c>
+      <c r="J15" s="13">
+        <v>0</v>
+      </c>
+      <c r="K15" s="13">
+        <v>0</v>
+      </c>
+      <c r="L15" s="13">
+        <v>0</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:13">
+      <c r="A16" s="12"/>
+      <c r="B16" s="13">
+        <v>5010</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="13">
+        <v>99</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H16" s="13">
+        <v>0</v>
+      </c>
+      <c r="I16" s="13">
+        <v>0</v>
+      </c>
+      <c r="J16" s="13">
+        <v>0</v>
+      </c>
+      <c r="K16" s="13">
+        <v>0</v>
+      </c>
+      <c r="L16" s="13">
+        <v>0</v>
+      </c>
+      <c r="M16" s="13" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="1:13">
+      <c r="A17" s="12"/>
+      <c r="B17" s="13">
+        <v>5011</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F17" s="13">
+        <v>99</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H17" s="13">
+        <v>0</v>
+      </c>
+      <c r="I17" s="13">
+        <v>0</v>
+      </c>
+      <c r="J17" s="13">
+        <v>0</v>
+      </c>
+      <c r="K17" s="13">
+        <v>0</v>
+      </c>
+      <c r="L17" s="13">
+        <v>0</v>
+      </c>
+      <c r="M17" s="13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="1:13">
+      <c r="A18" s="12"/>
+      <c r="B18" s="13">
+        <v>5012</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="13">
+        <v>99</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="13">
+        <v>0</v>
+      </c>
+      <c r="I18" s="13">
+        <v>0</v>
+      </c>
+      <c r="J18" s="13">
+        <v>0</v>
+      </c>
+      <c r="K18" s="13">
+        <v>0</v>
+      </c>
+      <c r="L18" s="13">
+        <v>0</v>
+      </c>
+      <c r="M18" s="13" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="1:13">
+      <c r="A19" s="12"/>
+      <c r="B19" s="13">
+        <v>5013</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F19" s="13">
+        <v>99</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="13">
+        <v>0</v>
+      </c>
+      <c r="I19" s="13">
+        <v>0</v>
+      </c>
+      <c r="J19" s="13">
+        <v>0</v>
+      </c>
+      <c r="K19" s="13">
+        <v>0</v>
+      </c>
+      <c r="L19" s="13">
+        <v>0</v>
+      </c>
+      <c r="M19" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="1:13">
+      <c r="A20" s="12"/>
+      <c r="B20" s="13">
+        <v>5014</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F20" s="13">
+        <v>99</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H20" s="13">
+        <v>0</v>
+      </c>
+      <c r="I20" s="13">
+        <v>0</v>
+      </c>
+      <c r="J20" s="13">
+        <v>0</v>
+      </c>
+      <c r="K20" s="13">
+        <v>0</v>
+      </c>
+      <c r="L20" s="13">
+        <v>0</v>
+      </c>
+      <c r="M20" s="13" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="1:13">
+      <c r="A21" s="12"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="M21" s="13"/>
+    </row>
+    <row r="22" customHeight="1" spans="1:13">
+      <c r="A22" s="12"/>
+      <c r="B22" s="13">
+        <v>5015</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="13">
+        <v>60</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H22" s="13">
+        <v>0</v>
+      </c>
+      <c r="I22" s="13">
+        <v>0</v>
+      </c>
+      <c r="J22" s="13">
+        <v>0</v>
+      </c>
+      <c r="K22" s="13">
+        <v>0</v>
+      </c>
+      <c r="L22" s="13">
+        <v>0</v>
+      </c>
+      <c r="M22" s="13" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="1:13">
+      <c r="A23" s="12"/>
+      <c r="B23" s="13">
+        <v>5016</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="13">
+        <v>60</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H23" s="13">
+        <v>0</v>
+      </c>
+      <c r="I23" s="13">
+        <v>0</v>
+      </c>
+      <c r="J23" s="13">
+        <v>0</v>
+      </c>
+      <c r="K23" s="13">
+        <v>0</v>
+      </c>
+      <c r="L23" s="13">
+        <v>0</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="1:13">
+      <c r="A24" s="12"/>
+      <c r="B24" s="13">
+        <v>5017</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="13">
+        <v>60</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" s="13">
+        <v>0</v>
+      </c>
+      <c r="I24" s="13">
+        <v>0</v>
+      </c>
+      <c r="J24" s="13">
+        <v>0</v>
+      </c>
+      <c r="K24" s="13">
+        <v>0</v>
+      </c>
+      <c r="L24" s="13">
+        <v>0</v>
+      </c>
+      <c r="M24" s="13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="1:13">
+      <c r="A25" s="12"/>
+      <c r="B25" s="13">
+        <v>5018</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="13">
+        <v>60</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H25" s="13">
+        <v>0</v>
+      </c>
+      <c r="I25" s="13">
+        <v>0</v>
+      </c>
+      <c r="J25" s="13">
+        <v>0</v>
+      </c>
+      <c r="K25" s="13">
+        <v>0</v>
+      </c>
+      <c r="L25" s="13">
+        <v>0</v>
+      </c>
+      <c r="M25" s="13" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:13">
+      <c r="A26" s="12"/>
+      <c r="B26" s="13">
+        <v>5019</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F26" s="13">
+        <v>60</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26" s="13">
+        <v>0</v>
+      </c>
+      <c r="I26" s="13">
+        <v>0</v>
+      </c>
+      <c r="J26" s="13">
+        <v>0</v>
+      </c>
+      <c r="K26" s="13">
+        <v>0</v>
+      </c>
+      <c r="L26" s="13">
+        <v>0</v>
+      </c>
+      <c r="M26" s="13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="1:13">
+      <c r="A27" s="12"/>
+      <c r="B27" s="13">
+        <v>5020</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F27" s="13">
+        <v>60</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H27" s="13">
+        <v>0</v>
+      </c>
+      <c r="I27" s="13">
+        <v>0</v>
+      </c>
+      <c r="J27" s="13">
+        <v>0</v>
+      </c>
+      <c r="K27" s="13">
+        <v>0</v>
+      </c>
+      <c r="L27" s="13">
+        <v>0</v>
+      </c>
+      <c r="M27" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="1:13">
+      <c r="A28" s="12"/>
+      <c r="B28" s="13">
+        <v>5021</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F28" s="13">
+        <v>60</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H28" s="13">
+        <v>0</v>
+      </c>
+      <c r="I28" s="13">
+        <v>0</v>
+      </c>
+      <c r="J28" s="13">
+        <v>0</v>
+      </c>
+      <c r="K28" s="13">
+        <v>0</v>
+      </c>
+      <c r="L28" s="13">
+        <v>0</v>
+      </c>
+      <c r="M28" s="13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="1:13">
+      <c r="A29" s="12"/>
+      <c r="B29" s="13">
+        <v>5022</v>
+      </c>
+      <c r="C29" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F29" s="13">
+        <v>60</v>
+      </c>
+      <c r="G29" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H29" s="13">
+        <v>0</v>
+      </c>
+      <c r="I29" s="13">
+        <v>0</v>
+      </c>
+      <c r="J29" s="13">
+        <v>0</v>
+      </c>
+      <c r="K29" s="13">
+        <v>0</v>
+      </c>
+      <c r="L29" s="13">
+        <v>0</v>
+      </c>
+      <c r="M29" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="1:13">
+      <c r="A30" s="12"/>
+      <c r="B30" s="13">
+        <v>5023</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F30" s="13">
+        <v>60</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H30" s="13">
+        <v>0</v>
+      </c>
+      <c r="I30" s="13">
+        <v>0</v>
+      </c>
+      <c r="J30" s="13">
+        <v>0</v>
+      </c>
+      <c r="K30" s="13">
+        <v>0</v>
+      </c>
+      <c r="L30" s="13">
+        <v>0</v>
+      </c>
+      <c r="M30" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="1:13">
+      <c r="A31" s="12"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="M31" s="13"/>
+    </row>
+    <row r="32" customHeight="1" spans="1:13">
+      <c r="A32" s="12"/>
+      <c r="B32" s="13">
+        <v>5024</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E32" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F32" s="13">
         <v>40</v>
       </c>
-      <c r="F6" s="7">
-        <v>99</v>
-      </c>
-      <c r="G6" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H6" s="7">
-        <v>0</v>
-      </c>
-      <c r="I6" s="7">
-        <v>0</v>
-      </c>
-      <c r="J6" s="7">
-        <v>0</v>
-      </c>
-      <c r="K6" s="7">
-        <v>0</v>
-      </c>
-      <c r="L6" s="1">
-        <v>0</v>
-      </c>
-      <c r="M6" s="7" t="s">
+      <c r="G32" s="13" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="7" customHeight="1" spans="1:13">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7">
-        <v>5003</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="7">
-        <v>99</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H7" s="7">
-        <v>0</v>
-      </c>
-      <c r="I7" s="7">
-        <v>0</v>
-      </c>
-      <c r="J7" s="7">
-        <v>0</v>
-      </c>
-      <c r="K7" s="7">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
-      <c r="M7" s="7" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8" customHeight="1" spans="1:13">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7">
-        <v>5004</v>
-      </c>
-      <c r="C8" s="7" t="s">
+      <c r="H32" s="13">
+        <v>0</v>
+      </c>
+      <c r="I32" s="13">
+        <v>0</v>
+      </c>
+      <c r="J32" s="13">
+        <v>0</v>
+      </c>
+      <c r="K32" s="13">
+        <v>0</v>
+      </c>
+      <c r="L32" s="13">
+        <v>0</v>
+      </c>
+      <c r="M32" s="13" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="1:13">
+      <c r="A33" s="12"/>
+      <c r="B33" s="13">
+        <v>5025</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E33" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="7">
-        <v>99</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H8" s="7">
-        <v>0</v>
-      </c>
-      <c r="I8" s="7">
-        <v>0</v>
-      </c>
-      <c r="J8" s="7">
-        <v>0</v>
-      </c>
-      <c r="K8" s="7">
-        <v>0</v>
-      </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-      <c r="M8" s="7" t="s">
+      <c r="F33" s="13">
+        <v>40</v>
+      </c>
+      <c r="G33" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H33" s="13">
+        <v>0</v>
+      </c>
+      <c r="I33" s="13">
+        <v>0</v>
+      </c>
+      <c r="J33" s="13">
+        <v>0</v>
+      </c>
+      <c r="K33" s="13">
+        <v>0</v>
+      </c>
+      <c r="L33" s="13">
+        <v>0</v>
+      </c>
+      <c r="M33" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="1:13">
+      <c r="A34" s="12"/>
+      <c r="B34" s="13">
+        <v>5026</v>
+      </c>
+      <c r="C34" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D34" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E34" s="13" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="9" customHeight="1" spans="1:13">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7">
-        <v>5005</v>
-      </c>
-      <c r="C9" s="7" t="s">
+      <c r="F34" s="13">
+        <v>40</v>
+      </c>
+      <c r="G34" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H34" s="13">
+        <v>0</v>
+      </c>
+      <c r="I34" s="13">
+        <v>0</v>
+      </c>
+      <c r="J34" s="13">
+        <v>0</v>
+      </c>
+      <c r="K34" s="13">
+        <v>0</v>
+      </c>
+      <c r="L34" s="13">
+        <v>0</v>
+      </c>
+      <c r="M34" s="13" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="1:13">
+      <c r="A35" s="12"/>
+      <c r="B35" s="13">
+        <v>5027</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D35" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E35" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F35" s="13">
+        <v>40</v>
+      </c>
+      <c r="G35" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H35" s="13">
+        <v>0</v>
+      </c>
+      <c r="I35" s="13">
+        <v>0</v>
+      </c>
+      <c r="J35" s="13">
+        <v>0</v>
+      </c>
+      <c r="K35" s="13">
+        <v>0</v>
+      </c>
+      <c r="L35" s="13">
+        <v>0</v>
+      </c>
+      <c r="M35" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="1:13">
+      <c r="A36" s="12"/>
+      <c r="B36" s="13">
+        <v>5028</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E36" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F36" s="13">
+        <v>40</v>
+      </c>
+      <c r="G36" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H36" s="13">
+        <v>0</v>
+      </c>
+      <c r="I36" s="13">
+        <v>0</v>
+      </c>
+      <c r="J36" s="13">
+        <v>0</v>
+      </c>
+      <c r="K36" s="13">
+        <v>0</v>
+      </c>
+      <c r="L36" s="13">
+        <v>0</v>
+      </c>
+      <c r="M36" s="13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="1:13">
+      <c r="A37" s="12"/>
+      <c r="B37" s="13">
+        <v>5029</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E37" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F37" s="13">
+        <v>40</v>
+      </c>
+      <c r="G37" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H37" s="13">
+        <v>0</v>
+      </c>
+      <c r="I37" s="13">
+        <v>0</v>
+      </c>
+      <c r="J37" s="13">
+        <v>0</v>
+      </c>
+      <c r="K37" s="13">
+        <v>0</v>
+      </c>
+      <c r="L37" s="13">
+        <v>0</v>
+      </c>
+      <c r="M37" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="1:13">
+      <c r="A38" s="12"/>
+      <c r="B38" s="13">
+        <v>5030</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D38" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E38" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F38" s="13">
+        <v>40</v>
+      </c>
+      <c r="G38" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H38" s="13">
+        <v>0</v>
+      </c>
+      <c r="I38" s="13">
+        <v>0</v>
+      </c>
+      <c r="J38" s="13">
+        <v>0</v>
+      </c>
+      <c r="K38" s="13">
+        <v>0</v>
+      </c>
+      <c r="L38" s="13">
+        <v>0</v>
+      </c>
+      <c r="M38" s="13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="1:13">
+      <c r="A39" s="12"/>
+      <c r="B39" s="13">
+        <v>5031</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D39" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E39" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F39" s="13">
+        <v>40</v>
+      </c>
+      <c r="G39" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H39" s="13">
+        <v>0</v>
+      </c>
+      <c r="I39" s="13">
+        <v>0</v>
+      </c>
+      <c r="J39" s="13">
+        <v>0</v>
+      </c>
+      <c r="K39" s="13">
+        <v>0</v>
+      </c>
+      <c r="L39" s="13">
+        <v>0</v>
+      </c>
+      <c r="M39" s="13" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="1:13">
+      <c r="A40" s="12"/>
+      <c r="B40" s="13">
+        <v>5032</v>
+      </c>
+      <c r="C40" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E40" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F40" s="13">
+        <v>40</v>
+      </c>
+      <c r="G40" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H40" s="13">
+        <v>0</v>
+      </c>
+      <c r="I40" s="13">
+        <v>0</v>
+      </c>
+      <c r="J40" s="13">
+        <v>0</v>
+      </c>
+      <c r="K40" s="13">
+        <v>0</v>
+      </c>
+      <c r="L40" s="13">
+        <v>0</v>
+      </c>
+      <c r="M40" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="1:13">
+      <c r="A41" s="12"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
+      <c r="H41" s="13"/>
+      <c r="I41" s="13"/>
+      <c r="J41" s="13"/>
+      <c r="K41" s="13"/>
+      <c r="M41" s="13"/>
+    </row>
+    <row r="42" customHeight="1" spans="1:13">
+      <c r="A42" s="12"/>
+      <c r="B42" s="13">
+        <v>5033</v>
+      </c>
+      <c r="C42" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E42" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D9" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="7">
-        <v>99</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H9" s="7">
-        <v>0</v>
-      </c>
-      <c r="I9" s="7">
-        <v>0</v>
-      </c>
-      <c r="J9" s="7">
-        <v>0</v>
-      </c>
-      <c r="K9" s="7">
-        <v>0</v>
-      </c>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
-      <c r="M9" s="7" t="s">
+      <c r="F42" s="13">
+        <v>20</v>
+      </c>
+      <c r="G42" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H42" s="13">
+        <v>0</v>
+      </c>
+      <c r="I42" s="13">
+        <v>0</v>
+      </c>
+      <c r="J42" s="13">
+        <v>0</v>
+      </c>
+      <c r="K42" s="13">
+        <v>0</v>
+      </c>
+      <c r="L42" s="13">
+        <v>0</v>
+      </c>
+      <c r="M42" s="13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="43" customHeight="1" spans="1:13">
+      <c r="A43" s="12"/>
+      <c r="B43" s="13">
+        <v>5034</v>
+      </c>
+      <c r="C43" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E43" s="13" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="10" customHeight="1" spans="1:13">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7">
-        <v>5101</v>
-      </c>
-      <c r="C10" s="7" t="s">
+      <c r="F43" s="13">
+        <v>20</v>
+      </c>
+      <c r="G43" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H43" s="13">
+        <v>0</v>
+      </c>
+      <c r="I43" s="13">
+        <v>0</v>
+      </c>
+      <c r="J43" s="13">
+        <v>0</v>
+      </c>
+      <c r="K43" s="13">
+        <v>0</v>
+      </c>
+      <c r="L43" s="13">
+        <v>0</v>
+      </c>
+      <c r="M43" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" customHeight="1" spans="1:13">
+      <c r="A44" s="12"/>
+      <c r="B44" s="13">
+        <v>5035</v>
+      </c>
+      <c r="C44" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D44" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E44" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F44" s="13">
+        <v>20</v>
+      </c>
+      <c r="G44" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H44" s="13">
+        <v>0</v>
+      </c>
+      <c r="I44" s="13">
+        <v>0</v>
+      </c>
+      <c r="J44" s="13">
+        <v>0</v>
+      </c>
+      <c r="K44" s="13">
+        <v>0</v>
+      </c>
+      <c r="L44" s="13">
+        <v>0</v>
+      </c>
+      <c r="M44" s="13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="45" customHeight="1" spans="1:13">
+      <c r="A45" s="12"/>
+      <c r="B45" s="13">
+        <v>5036</v>
+      </c>
+      <c r="C45" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D45" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E45" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F45" s="13">
+        <v>20</v>
+      </c>
+      <c r="G45" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H45" s="13">
+        <v>0</v>
+      </c>
+      <c r="I45" s="13">
+        <v>0</v>
+      </c>
+      <c r="J45" s="13">
+        <v>0</v>
+      </c>
+      <c r="K45" s="13">
+        <v>0</v>
+      </c>
+      <c r="L45" s="13">
+        <v>0</v>
+      </c>
+      <c r="M45" s="13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" customHeight="1" spans="1:13">
+      <c r="A46" s="12"/>
+      <c r="B46" s="13">
+        <v>5037</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="D46" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E46" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F46" s="13">
+        <v>20</v>
+      </c>
+      <c r="G46" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H46" s="13">
+        <v>0</v>
+      </c>
+      <c r="I46" s="13">
+        <v>0</v>
+      </c>
+      <c r="J46" s="13">
+        <v>0</v>
+      </c>
+      <c r="K46" s="13">
+        <v>0</v>
+      </c>
+      <c r="L46" s="13">
+        <v>0</v>
+      </c>
+      <c r="M46" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="47" customHeight="1" spans="1:13">
+      <c r="A47" s="12"/>
+      <c r="B47" s="13">
+        <v>5038</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E47" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F47" s="13">
+        <v>20</v>
+      </c>
+      <c r="G47" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H47" s="13">
+        <v>0</v>
+      </c>
+      <c r="I47" s="13">
+        <v>0</v>
+      </c>
+      <c r="J47" s="13">
+        <v>0</v>
+      </c>
+      <c r="K47" s="13">
+        <v>0</v>
+      </c>
+      <c r="L47" s="13">
+        <v>0</v>
+      </c>
+      <c r="M47" s="13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="48" customHeight="1" spans="1:13">
+      <c r="A48" s="12"/>
+      <c r="B48" s="13">
+        <v>5039</v>
+      </c>
+      <c r="C48" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D48" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E48" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F48" s="13">
+        <v>20</v>
+      </c>
+      <c r="G48" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H48" s="13">
+        <v>0</v>
+      </c>
+      <c r="I48" s="13">
+        <v>0</v>
+      </c>
+      <c r="J48" s="13">
+        <v>0</v>
+      </c>
+      <c r="K48" s="13">
+        <v>0</v>
+      </c>
+      <c r="L48" s="13">
+        <v>0</v>
+      </c>
+      <c r="M48" s="13" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="49" customHeight="1" spans="1:13">
+      <c r="A49" s="12"/>
+      <c r="B49" s="13">
+        <v>5040</v>
+      </c>
+      <c r="C49" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="D49" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E49" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F49" s="13">
+        <v>20</v>
+      </c>
+      <c r="G49" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H49" s="13">
+        <v>0</v>
+      </c>
+      <c r="I49" s="13">
+        <v>0</v>
+      </c>
+      <c r="J49" s="13">
+        <v>0</v>
+      </c>
+      <c r="K49" s="13">
+        <v>0</v>
+      </c>
+      <c r="L49" s="13">
+        <v>0</v>
+      </c>
+      <c r="M49" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" customHeight="1" spans="1:13">
+      <c r="A50" s="12"/>
+      <c r="B50" s="13">
+        <v>5041</v>
+      </c>
+      <c r="C50" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D50" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E50" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F50" s="13">
+        <v>20</v>
+      </c>
+      <c r="G50" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H50" s="13">
+        <v>0</v>
+      </c>
+      <c r="I50" s="13">
+        <v>0</v>
+      </c>
+      <c r="J50" s="13">
+        <v>0</v>
+      </c>
+      <c r="K50" s="13">
+        <v>0</v>
+      </c>
+      <c r="L50" s="13">
+        <v>0</v>
+      </c>
+      <c r="M50" s="13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="51" customHeight="1" spans="1:13">
+      <c r="A51" s="12"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
+      <c r="I51" s="13"/>
+      <c r="J51" s="13"/>
+      <c r="K51" s="13"/>
+      <c r="M51" s="13"/>
+    </row>
+    <row r="52" customHeight="1" spans="1:13">
+      <c r="A52" s="12"/>
+      <c r="B52" s="13">
+        <v>5043</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E52" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="7" t="s">
+      <c r="F52" s="13">
+        <v>1</v>
+      </c>
+      <c r="G52" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H52" s="13">
+        <v>0</v>
+      </c>
+      <c r="I52" s="13">
+        <v>0</v>
+      </c>
+      <c r="J52" s="13">
+        <v>0</v>
+      </c>
+      <c r="K52" s="13">
+        <v>0</v>
+      </c>
+      <c r="L52" s="13">
+        <v>0</v>
+      </c>
+      <c r="M52" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="1:13">
+      <c r="A53" s="12"/>
+      <c r="B53" s="13">
+        <v>5044</v>
+      </c>
+      <c r="C53" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D53" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F10" s="7">
+      <c r="E53" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F53" s="13">
         <v>1</v>
       </c>
-      <c r="G10" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H10" s="7">
-        <v>0</v>
-      </c>
-      <c r="I10" s="7">
-        <v>0</v>
-      </c>
-      <c r="J10" s="7">
-        <v>5</v>
-      </c>
-      <c r="K10" s="7">
-        <v>0</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
-      <c r="M10" s="7" t="s">
+      <c r="G53" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H53" s="13">
+        <v>0</v>
+      </c>
+      <c r="I53" s="13">
+        <v>0</v>
+      </c>
+      <c r="J53" s="13">
+        <v>0</v>
+      </c>
+      <c r="K53" s="13">
+        <v>0</v>
+      </c>
+      <c r="L53" s="13">
+        <v>0</v>
+      </c>
+      <c r="M53" s="13" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="54" customHeight="1" spans="1:13">
+      <c r="A54" s="12"/>
+      <c r="B54" s="13">
+        <v>5045</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E54" s="13" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="11" customHeight="1" spans="1:13">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7">
-        <v>5102</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" s="7">
+      <c r="F54" s="13">
         <v>1</v>
       </c>
-      <c r="G11" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H11" s="7">
-        <v>0</v>
-      </c>
-      <c r="I11" s="7">
-        <v>10</v>
-      </c>
-      <c r="J11" s="7">
-        <v>0</v>
-      </c>
-      <c r="K11" s="7">
-        <v>8</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
-      <c r="M11" s="7" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="1:13">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7">
-        <v>5201</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="F12" s="7">
+      <c r="G54" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H54" s="13">
+        <v>0</v>
+      </c>
+      <c r="I54" s="13">
+        <v>0</v>
+      </c>
+      <c r="J54" s="13">
+        <v>0</v>
+      </c>
+      <c r="K54" s="13">
+        <v>0</v>
+      </c>
+      <c r="L54" s="13">
+        <v>0</v>
+      </c>
+      <c r="M54" s="13" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="55" customHeight="1" spans="1:13">
+      <c r="A55" s="12"/>
+      <c r="B55" s="13">
+        <v>5046</v>
+      </c>
+      <c r="C55" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E55" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F55" s="13">
         <v>1</v>
       </c>
-      <c r="G12" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="H12" s="7">
-        <v>20</v>
-      </c>
-      <c r="I12" s="7">
-        <v>0</v>
-      </c>
-      <c r="J12" s="7">
-        <v>0</v>
-      </c>
-      <c r="K12" s="7">
-        <v>0</v>
-      </c>
-      <c r="L12" s="1">
+      <c r="G55" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H55" s="13">
+        <v>0</v>
+      </c>
+      <c r="I55" s="13">
+        <v>0</v>
+      </c>
+      <c r="J55" s="13">
+        <v>0</v>
+      </c>
+      <c r="K55" s="13">
+        <v>0</v>
+      </c>
+      <c r="L55" s="13">
+        <v>0</v>
+      </c>
+      <c r="M55" s="13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="1:13">
+      <c r="A56" s="12"/>
+      <c r="B56" s="13">
+        <v>5047</v>
+      </c>
+      <c r="C56" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E56" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F56" s="13">
         <v>1</v>
       </c>
-      <c r="M12" s="7" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:13">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7">
-        <v>5202</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F13" s="7">
+      <c r="G56" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H56" s="13">
+        <v>0</v>
+      </c>
+      <c r="I56" s="13">
+        <v>0</v>
+      </c>
+      <c r="J56" s="13">
+        <v>0</v>
+      </c>
+      <c r="K56" s="13">
+        <v>0</v>
+      </c>
+      <c r="L56" s="13">
+        <v>0</v>
+      </c>
+      <c r="M56" s="13" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="57" customHeight="1" spans="1:13">
+      <c r="A57" s="12"/>
+      <c r="B57" s="13">
+        <v>5048</v>
+      </c>
+      <c r="C57" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E57" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F57" s="13">
         <v>1</v>
       </c>
-      <c r="G13" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="H13" s="7">
-        <v>10</v>
-      </c>
-      <c r="I13" s="7">
-        <v>30</v>
-      </c>
-      <c r="J13" s="7">
-        <v>0</v>
-      </c>
-      <c r="K13" s="7">
-        <v>5</v>
-      </c>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:13">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7">
-        <v>5301</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="7" t="s">
+      <c r="G57" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H57" s="13">
+        <v>0</v>
+      </c>
+      <c r="I57" s="13">
+        <v>0</v>
+      </c>
+      <c r="J57" s="13">
+        <v>0</v>
+      </c>
+      <c r="K57" s="13">
+        <v>0</v>
+      </c>
+      <c r="L57" s="13">
+        <v>0</v>
+      </c>
+      <c r="M57" s="13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="58" customHeight="1" spans="1:13">
+      <c r="A58" s="12"/>
+      <c r="B58" s="13">
+        <v>5049</v>
+      </c>
+      <c r="C58" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D58" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="F14" s="7">
-        <v>10</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" s="7">
-        <v>0</v>
-      </c>
-      <c r="I14" s="7">
-        <v>0</v>
-      </c>
-      <c r="J14" s="7">
-        <v>0</v>
-      </c>
-      <c r="K14" s="7">
-        <v>0</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="7" t="s">
-        <v>54</v>
-      </c>
+      <c r="E58" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F58" s="13">
+        <v>1</v>
+      </c>
+      <c r="G58" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H58" s="13">
+        <v>0</v>
+      </c>
+      <c r="I58" s="13">
+        <v>0</v>
+      </c>
+      <c r="J58" s="13">
+        <v>0</v>
+      </c>
+      <c r="K58" s="13">
+        <v>0</v>
+      </c>
+      <c r="L58" s="13">
+        <v>0</v>
+      </c>
+      <c r="M58" s="13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="59" customHeight="1" spans="1:13">
+      <c r="A59" s="12"/>
+      <c r="B59" s="13">
+        <v>5050</v>
+      </c>
+      <c r="C59" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E59" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F59" s="13">
+        <v>1</v>
+      </c>
+      <c r="G59" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H59" s="13">
+        <v>0</v>
+      </c>
+      <c r="I59" s="13">
+        <v>0</v>
+      </c>
+      <c r="J59" s="13">
+        <v>0</v>
+      </c>
+      <c r="K59" s="13">
+        <v>0</v>
+      </c>
+      <c r="L59" s="13">
+        <v>0</v>
+      </c>
+      <c r="M59" s="13" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" customHeight="1" spans="1:13">
+      <c r="A60" s="12"/>
+      <c r="B60" s="13">
+        <v>5051</v>
+      </c>
+      <c r="C60" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="E60" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F60" s="13">
+        <v>1</v>
+      </c>
+      <c r="G60" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H60" s="13">
+        <v>0</v>
+      </c>
+      <c r="I60" s="13">
+        <v>0</v>
+      </c>
+      <c r="J60" s="13">
+        <v>0</v>
+      </c>
+      <c r="K60" s="13">
+        <v>0</v>
+      </c>
+      <c r="L60" s="13">
+        <v>0</v>
+      </c>
+      <c r="M60" s="13" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="61" customHeight="1" spans="1:13">
+      <c r="A61" s="12"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
+      <c r="I61" s="13"/>
+      <c r="J61" s="13"/>
+      <c r="K61" s="13"/>
+      <c r="M61" s="13"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M28"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="20" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="9.16666666666667" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10.25" style="18" customWidth="1"/>
+    <col min="3" max="3" width="15.0833333333333" style="19" customWidth="1"/>
+    <col min="4" max="4" width="15.4166666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="18" customWidth="1"/>
+    <col min="6" max="6" width="12.75" style="18" customWidth="1"/>
+    <col min="7" max="7" width="21.1666666666667" style="2" customWidth="1"/>
+    <col min="8" max="9" width="12.75" style="2" customWidth="1"/>
+    <col min="10" max="11" width="10.3333333333333" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12.75" style="2" customWidth="1"/>
+    <col min="13" max="13" width="30.8333333333333" style="17" customWidth="1"/>
+    <col min="14" max="16384" width="8.66666666666667" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="5" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="M3" s="7"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customHeight="1" spans="1:13">
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13"/>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13">
+        <v>5101</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="13">
+        <v>1</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H6" s="13">
+        <v>0</v>
+      </c>
+      <c r="I6" s="13">
+        <v>0</v>
+      </c>
+      <c r="J6" s="13">
+        <v>5</v>
+      </c>
+      <c r="K6" s="13">
+        <v>0</v>
+      </c>
+      <c r="L6" s="13">
+        <v>0</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A7" s="12"/>
+      <c r="B7" s="13">
+        <v>5102</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="13">
+        <v>1</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H7" s="13">
+        <v>0</v>
+      </c>
+      <c r="I7" s="13">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13">
+        <v>8</v>
+      </c>
+      <c r="K7" s="13">
+        <v>8</v>
+      </c>
+      <c r="L7" s="13">
+        <v>0</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:13">
+      <c r="B8" s="13">
+        <v>5103</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="13">
+        <v>1</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H8" s="13">
+        <v>0</v>
+      </c>
+      <c r="I8" s="13">
+        <v>0</v>
+      </c>
+      <c r="J8" s="13">
+        <v>10</v>
+      </c>
+      <c r="K8" s="13">
+        <v>0</v>
+      </c>
+      <c r="L8" s="13">
+        <v>0</v>
+      </c>
+      <c r="M8" s="13" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:13">
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+      <c r="F9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="13"/>
+      <c r="L9" s="13"/>
+      <c r="M9" s="13"/>
+    </row>
+    <row r="10" customHeight="1" spans="1:13">
+      <c r="B10" s="13">
+        <v>5104</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="13">
+        <v>1</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H10" s="13">
+        <v>0</v>
+      </c>
+      <c r="I10" s="13">
+        <v>0</v>
+      </c>
+      <c r="J10" s="13">
+        <v>7</v>
+      </c>
+      <c r="K10" s="13">
+        <v>0</v>
+      </c>
+      <c r="L10" s="13">
+        <v>0</v>
+      </c>
+      <c r="M10" s="13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:13">
+      <c r="B11" s="13">
+        <v>5105</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" s="13">
+        <v>1</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="13">
+        <v>0</v>
+      </c>
+      <c r="I11" s="13">
+        <v>0</v>
+      </c>
+      <c r="J11" s="13">
+        <v>12</v>
+      </c>
+      <c r="K11" s="13">
+        <v>0</v>
+      </c>
+      <c r="L11" s="13">
+        <v>0</v>
+      </c>
+      <c r="M11" s="13" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:13">
+      <c r="B12" s="13">
+        <v>5106</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="13">
+        <v>1</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H12" s="13">
+        <v>0</v>
+      </c>
+      <c r="I12" s="13">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13">
+        <v>15</v>
+      </c>
+      <c r="K12" s="13">
+        <v>0</v>
+      </c>
+      <c r="L12" s="13">
+        <v>0</v>
+      </c>
+      <c r="M12" s="13" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:13">
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="13"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="13"/>
+      <c r="M13" s="13"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:13">
+      <c r="B14" s="13">
+        <v>5107</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="13">
+        <v>1</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H14" s="13">
+        <v>0</v>
+      </c>
+      <c r="I14" s="13">
+        <v>0</v>
+      </c>
+      <c r="J14" s="13">
+        <v>10</v>
+      </c>
+      <c r="K14" s="13">
+        <v>0</v>
+      </c>
+      <c r="L14" s="13">
+        <v>0</v>
+      </c>
+      <c r="M14" s="13" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:13">
+      <c r="B15" s="13">
+        <v>5108</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="13">
+        <v>1</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="13">
+        <v>0</v>
+      </c>
+      <c r="I15" s="13">
+        <v>0</v>
+      </c>
+      <c r="J15" s="13">
+        <v>15</v>
+      </c>
+      <c r="K15" s="13">
+        <v>0</v>
+      </c>
+      <c r="L15" s="13">
+        <v>0</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:13">
+      <c r="B16" s="13">
+        <v>5109</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="13">
+        <v>1</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H16" s="13">
+        <v>0</v>
+      </c>
+      <c r="I16" s="13">
+        <v>0</v>
+      </c>
+      <c r="J16" s="13">
+        <v>20</v>
+      </c>
+      <c r="K16" s="13">
+        <v>0</v>
+      </c>
+      <c r="L16" s="13">
+        <v>0</v>
+      </c>
+      <c r="M16" s="13" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="2:13">
+      <c r="B17" s="13"/>
+      <c r="C17" s="13"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
+      <c r="F17" s="13"/>
+      <c r="G17" s="13"/>
+      <c r="H17" s="13"/>
+      <c r="I17" s="13"/>
+      <c r="J17" s="13"/>
+      <c r="K17" s="13"/>
+      <c r="L17" s="13"/>
+      <c r="M17" s="13"/>
+    </row>
+    <row r="18" customHeight="1" spans="2:13">
+      <c r="B18" s="13">
+        <v>5110</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F18" s="13">
+        <v>1</v>
+      </c>
+      <c r="G18" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H18" s="13">
+        <v>0</v>
+      </c>
+      <c r="I18" s="13">
+        <v>0</v>
+      </c>
+      <c r="J18" s="13">
+        <v>0</v>
+      </c>
+      <c r="K18" s="13">
+        <v>6</v>
+      </c>
+      <c r="L18" s="13">
+        <v>0</v>
+      </c>
+      <c r="M18" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="2:13">
+      <c r="B19" s="13">
+        <v>5111</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E19" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F19" s="13">
+        <v>1</v>
+      </c>
+      <c r="G19" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H19" s="13">
+        <v>0</v>
+      </c>
+      <c r="I19" s="13">
+        <v>0</v>
+      </c>
+      <c r="J19" s="13">
+        <v>0</v>
+      </c>
+      <c r="K19" s="13">
+        <v>10</v>
+      </c>
+      <c r="L19" s="13">
+        <v>0</v>
+      </c>
+      <c r="M19" s="13" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="2:13">
+      <c r="B20" s="13">
+        <v>5112</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F20" s="13">
+        <v>1</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H20" s="13">
+        <v>0</v>
+      </c>
+      <c r="I20" s="13">
+        <v>0</v>
+      </c>
+      <c r="J20" s="13">
+        <v>0</v>
+      </c>
+      <c r="K20" s="13">
+        <v>13</v>
+      </c>
+      <c r="L20" s="13">
+        <v>0</v>
+      </c>
+      <c r="M20" s="13" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" customHeight="1" spans="2:13">
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
+    </row>
+    <row r="22" customHeight="1" spans="2:13">
+      <c r="B22" s="13">
+        <v>5113</v>
+      </c>
+      <c r="C22" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D22" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="13">
+        <v>1</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H22" s="13">
+        <v>0</v>
+      </c>
+      <c r="I22" s="13">
+        <v>0</v>
+      </c>
+      <c r="J22" s="13">
+        <v>0</v>
+      </c>
+      <c r="K22" s="13">
+        <v>9</v>
+      </c>
+      <c r="L22" s="13">
+        <v>0</v>
+      </c>
+      <c r="M22" s="13" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="2:13">
+      <c r="B23" s="13">
+        <v>5114</v>
+      </c>
+      <c r="C23" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F23" s="13">
+        <v>1</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H23" s="13">
+        <v>0</v>
+      </c>
+      <c r="I23" s="13">
+        <v>0</v>
+      </c>
+      <c r="J23" s="13">
+        <v>0</v>
+      </c>
+      <c r="K23" s="13">
+        <v>14</v>
+      </c>
+      <c r="L23" s="13">
+        <v>0</v>
+      </c>
+      <c r="M23" s="13" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="2:13">
+      <c r="B24" s="13">
+        <v>5115</v>
+      </c>
+      <c r="C24" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E24" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F24" s="13">
+        <v>1</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H24" s="13">
+        <v>0</v>
+      </c>
+      <c r="I24" s="13">
+        <v>0</v>
+      </c>
+      <c r="J24" s="13">
+        <v>0</v>
+      </c>
+      <c r="K24" s="13">
+        <v>20</v>
+      </c>
+      <c r="L24" s="13">
+        <v>0</v>
+      </c>
+      <c r="M24" s="13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="2:13">
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
+      <c r="H25" s="13"/>
+      <c r="I25" s="13"/>
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+      <c r="L25" s="13"/>
+      <c r="M25" s="13"/>
+    </row>
+    <row r="26" customHeight="1" spans="2:13">
+      <c r="B26" s="13">
+        <v>5116</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E26" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="13">
+        <v>1</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" s="13">
+        <v>0</v>
+      </c>
+      <c r="I26" s="13">
+        <v>0</v>
+      </c>
+      <c r="J26" s="13">
+        <v>0</v>
+      </c>
+      <c r="K26" s="13">
+        <v>7</v>
+      </c>
+      <c r="L26" s="13">
+        <v>0</v>
+      </c>
+      <c r="M26" s="13" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="2:13">
+      <c r="B27" s="13">
+        <v>5117</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F27" s="13">
+        <v>1</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27" s="13">
+        <v>0</v>
+      </c>
+      <c r="I27" s="13">
+        <v>0</v>
+      </c>
+      <c r="J27" s="13">
+        <v>0</v>
+      </c>
+      <c r="K27" s="13">
+        <v>18</v>
+      </c>
+      <c r="L27" s="13">
+        <v>0</v>
+      </c>
+      <c r="M27" s="13" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="2:13">
+      <c r="B28" s="13">
+        <v>5118</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F28" s="13">
+        <v>1</v>
+      </c>
+      <c r="G28" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="H28" s="13">
+        <v>0</v>
+      </c>
+      <c r="I28" s="13">
+        <v>0</v>
+      </c>
+      <c r="J28" s="13">
+        <v>0</v>
+      </c>
+      <c r="K28" s="13">
+        <v>25</v>
+      </c>
+      <c r="L28" s="13">
+        <v>0</v>
+      </c>
+      <c r="M28" s="13" t="s">
+        <v>112</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M16"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="20" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="9.16666666666667" style="17" customWidth="1"/>
+    <col min="2" max="2" width="9.5" style="18" customWidth="1"/>
+    <col min="3" max="3" width="14.1666666666667" style="18" customWidth="1"/>
+    <col min="4" max="4" width="16.1666666666667" style="18" customWidth="1"/>
+    <col min="5" max="5" width="8.08333333333333" style="18" customWidth="1"/>
+    <col min="6" max="6" width="12.75" style="18" customWidth="1"/>
+    <col min="7" max="7" width="21.1666666666667" style="18" customWidth="1"/>
+    <col min="8" max="9" width="12.75" style="18" customWidth="1"/>
+    <col min="10" max="11" width="10.3333333333333" style="18" customWidth="1"/>
+    <col min="12" max="12" width="12.75" style="18" customWidth="1"/>
+    <col min="13" max="13" width="30.8333333333333" style="18" customWidth="1"/>
+    <col min="14" max="16384" width="8.66666666666667" style="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="16" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" s="16" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" s="16" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+    </row>
+    <row r="4" s="16" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" s="16" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13">
+        <v>5201</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="13">
+        <v>1</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H6" s="13">
+        <v>20</v>
+      </c>
+      <c r="I6" s="13">
+        <v>0</v>
+      </c>
+      <c r="J6" s="13">
+        <v>0</v>
+      </c>
+      <c r="K6" s="13">
+        <v>0</v>
+      </c>
+      <c r="L6" s="14">
+        <v>0</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="7" s="16" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A7" s="12"/>
+      <c r="B7" s="13">
+        <v>5202</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="13">
+        <v>1</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H7" s="13">
+        <v>30</v>
+      </c>
+      <c r="I7" s="13">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13">
+        <v>0</v>
+      </c>
+      <c r="K7" s="13">
+        <v>5</v>
+      </c>
+      <c r="L7" s="14">
+        <v>0</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:13">
+      <c r="B8" s="18">
+        <v>5203</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="18">
+        <v>1</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H8" s="18">
+        <v>40</v>
+      </c>
+      <c r="I8" s="18">
+        <v>10</v>
+      </c>
+      <c r="J8" s="18">
+        <v>0</v>
+      </c>
+      <c r="K8" s="18">
+        <v>0</v>
+      </c>
+      <c r="L8" s="18">
+        <v>0</v>
+      </c>
+      <c r="M8" s="13" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="1:13">
+      <c r="B9" s="18">
+        <v>5204</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="18">
+        <v>1</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H9" s="18">
+        <v>50</v>
+      </c>
+      <c r="I9" s="18">
+        <v>15</v>
+      </c>
+      <c r="J9" s="18">
+        <v>0</v>
+      </c>
+      <c r="K9" s="18">
+        <v>0</v>
+      </c>
+      <c r="L9" s="18">
+        <v>0</v>
+      </c>
+      <c r="M9" s="13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="1:13">
+      <c r="B10" s="18">
+        <v>5205</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="18">
+        <v>1</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H10" s="18">
+        <v>60</v>
+      </c>
+      <c r="I10" s="18">
+        <v>40</v>
+      </c>
+      <c r="J10" s="18">
+        <v>5</v>
+      </c>
+      <c r="K10" s="18">
+        <v>0</v>
+      </c>
+      <c r="L10" s="18">
+        <v>0</v>
+      </c>
+      <c r="M10" s="13" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:13">
+      <c r="C11" s="13"/>
+      <c r="M11" s="13"/>
+    </row>
+    <row r="12" customHeight="1" spans="1:13">
+      <c r="B12" s="18">
+        <v>5206</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="13">
+        <v>1</v>
+      </c>
+      <c r="G12" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H12" s="18">
+        <v>10</v>
+      </c>
+      <c r="I12" s="18">
+        <v>10</v>
+      </c>
+      <c r="J12" s="18">
+        <v>0</v>
+      </c>
+      <c r="K12" s="18">
+        <v>1</v>
+      </c>
+      <c r="L12" s="18">
+        <v>2</v>
+      </c>
+      <c r="M12" s="13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:13">
+      <c r="B13" s="18">
+        <v>5207</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" s="13">
+        <v>1</v>
+      </c>
+      <c r="G13" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H13" s="18">
+        <v>20</v>
+      </c>
+      <c r="I13" s="18">
+        <v>25</v>
+      </c>
+      <c r="J13" s="18">
+        <v>0</v>
+      </c>
+      <c r="K13" s="18">
+        <v>2</v>
+      </c>
+      <c r="L13" s="18">
+        <v>2</v>
+      </c>
+      <c r="M13" s="13" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:13">
+      <c r="B14" s="18">
+        <v>5208</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="F14" s="18">
+        <v>1</v>
+      </c>
+      <c r="G14" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H14" s="18">
+        <v>25</v>
+      </c>
+      <c r="I14" s="18">
+        <v>40</v>
+      </c>
+      <c r="J14" s="18">
+        <v>0</v>
+      </c>
+      <c r="K14" s="18">
+        <v>3</v>
+      </c>
+      <c r="L14" s="18">
+        <v>2</v>
+      </c>
+      <c r="M14" s="13" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="1:13">
+      <c r="B15" s="18">
+        <v>5209</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="16" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="18">
+        <v>1</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H15" s="18">
+        <v>40</v>
+      </c>
+      <c r="I15" s="18">
+        <v>60</v>
+      </c>
+      <c r="J15" s="18">
+        <v>0</v>
+      </c>
+      <c r="K15" s="18">
+        <v>4</v>
+      </c>
+      <c r="L15" s="18">
+        <v>2</v>
+      </c>
+      <c r="M15" s="13" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="1:13">
+      <c r="B16" s="18">
+        <v>5210</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>47</v>
+      </c>
+      <c r="F16" s="18">
+        <v>1</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="H16" s="18">
+        <v>45</v>
+      </c>
+      <c r="I16" s="18">
+        <v>80</v>
+      </c>
+      <c r="J16" s="18">
+        <v>0</v>
+      </c>
+      <c r="K16" s="18">
+        <v>5</v>
+      </c>
+      <c r="L16" s="18">
+        <v>2</v>
+      </c>
+      <c r="M16" s="13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="20" customHeight="1"/>
+  <cols>
+    <col min="1" max="1" width="9.16666666666667" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.91666666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="12.6666666666667" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17.25" style="2" customWidth="1"/>
+    <col min="5" max="5" width="8.08333333333333" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.75" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.1666666666667" style="2" customWidth="1"/>
+    <col min="8" max="9" width="12.75" style="2" customWidth="1"/>
+    <col min="10" max="11" width="10.3333333333333" style="2" customWidth="1"/>
+    <col min="12" max="12" width="12.75" style="2" customWidth="1"/>
+    <col min="13" max="13" width="30.8333333333333" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="8.66666666666667" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A2" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="K3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="8"/>
+      <c r="M3" s="8"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A4" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="H4" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="10" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13">
+        <v>5301</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="13">
+        <v>10</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="13">
+        <v>0</v>
+      </c>
+      <c r="I6" s="13">
+        <v>0</v>
+      </c>
+      <c r="J6" s="13">
+        <v>0</v>
+      </c>
+      <c r="K6" s="13">
+        <v>0</v>
+      </c>
+      <c r="L6" s="14">
+        <v>0</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A7" s="15"/>
+      <c r="B7" s="14">
+        <v>5302</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" s="14">
+        <v>8</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H7" s="13">
+        <v>0</v>
+      </c>
+      <c r="I7" s="13">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13">
+        <v>0</v>
+      </c>
+      <c r="K7" s="13">
+        <v>0</v>
+      </c>
+      <c r="L7" s="13">
+        <v>0</v>
+      </c>
+      <c r="M7" s="14" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A8" s="15"/>
+      <c r="B8" s="14">
+        <v>5303</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="14">
+        <v>7</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="13">
+        <v>0</v>
+      </c>
+      <c r="I8" s="13">
+        <v>0</v>
+      </c>
+      <c r="J8" s="13">
+        <v>0</v>
+      </c>
+      <c r="K8" s="13">
+        <v>0</v>
+      </c>
+      <c r="L8" s="13">
+        <v>0</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A9" s="15"/>
+      <c r="B9" s="14">
+        <v>5304</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" s="14">
+        <v>6</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H9" s="13">
+        <v>0</v>
+      </c>
+      <c r="I9" s="13">
+        <v>0</v>
+      </c>
+      <c r="J9" s="13">
+        <v>0</v>
+      </c>
+      <c r="K9" s="13">
+        <v>0</v>
+      </c>
+      <c r="L9" s="13">
+        <v>0</v>
+      </c>
+      <c r="M9" s="14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="1:13">
+      <c r="A10" s="15"/>
+      <c r="B10" s="14">
+        <v>5305</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="14">
+        <v>5</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="H10" s="13">
+        <v>0</v>
+      </c>
+      <c r="I10" s="13">
+        <v>0</v>
+      </c>
+      <c r="J10" s="13">
+        <v>0</v>
+      </c>
+      <c r="K10" s="13">
+        <v>0</v>
+      </c>
+      <c r="L10" s="13">
+        <v>0</v>
+      </c>
+      <c r="M10" s="14" t="s">
+        <v>136</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>